--- a/گزارش/لیست شرکتها/TradeMap Companies Database - Verified & Completed.xlsx
+++ b/گزارش/لیست شرکتها/TradeMap Companies Database - Verified & Completed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\مهرداد\سپهران\ایمیل بازاریابی\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DA5B45-63C3-46F1-B327-88C791F6B16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B14BAC-6825-474F-9850-00AAD03A8D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Verified Companies" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Companies'!$A$1:$H$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Companies'!$A$1:$H$152</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="755">
   <si>
     <t>English Name</t>
   </si>
@@ -139,33 +139,6 @@
     <t>https://dempseyeurope.com</t>
   </si>
   <si>
-    <t>AMPERE INDUSTRIE</t>
-  </si>
-  <si>
-    <t>Unclear — likely industrial chemical distribution based on Trade Map HS listing</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>SEREZIN DU RHONE, France</t>
-  </si>
-  <si>
-    <t>+33 4 78 02 32 00</t>
-  </si>
-  <si>
-    <t>marie@ampere.com</t>
-  </si>
-  <si>
-    <t>https://www.ampere.com</t>
-  </si>
-  <si>
-    <t>SAINT OUEN L'AUMONE, France</t>
-  </si>
-  <si>
-    <t>+33 1 34 32 38 00</t>
-  </si>
-  <si>
     <t>AVANTOR PERFORMANCE MATERIALS POLAND SPÓLKA AKCYJNA</t>
   </si>
   <si>
@@ -673,24 +646,9 @@
     <t>https://www.caldic.com</t>
   </si>
   <si>
-    <t>Cargill</t>
-  </si>
-  <si>
-    <t>⭐ Food and agribusiness — one of the world's largest food/agriculture companies</t>
-  </si>
-  <si>
     <t>Food (high confidence)</t>
   </si>
   <si>
-    <t>Martorell, Spain</t>
-  </si>
-  <si>
-    <t>+34 93 773 38 00</t>
-  </si>
-  <si>
-    <t>https://www.cargill.es</t>
-  </si>
-  <si>
     <t>CBC Europe GmbH</t>
   </si>
   <si>
@@ -757,9 +715,6 @@
     <t>https://www.brenntag.com/en-de/industries/food-and-nutrition/</t>
   </si>
   <si>
-    <t>Chemical distribution (explicit in name)</t>
-  </si>
-  <si>
     <t>CHIMITEX S.P.A</t>
   </si>
   <si>
@@ -838,21 +793,6 @@
     <t>https://comercialgodo.com</t>
   </si>
   <si>
-    <t>Comor SA</t>
-  </si>
-  <si>
-    <t>Niederanven, Luxembourg</t>
-  </si>
-  <si>
-    <t>+352 26 34 71 1</t>
-  </si>
-  <si>
-    <t>contact@comor.lu</t>
-  </si>
-  <si>
-    <t>https://www.comor.lu</t>
-  </si>
-  <si>
     <t>COMPANIA INDIILOR ORIENTALE PROD SRL</t>
   </si>
   <si>
@@ -1027,21 +967,6 @@
     <t>https://www.ekoprom.hr</t>
   </si>
   <si>
-    <t>Emix Przedsiebiorstwo Produkcyjno-Handlowe; Stanislaw Pacek</t>
-  </si>
-  <si>
-    <t>Rypin, Poland</t>
-  </si>
-  <si>
-    <t>+48 54 280 20 13</t>
-  </si>
-  <si>
-    <t>biuro@emix.com.pl</t>
-  </si>
-  <si>
-    <t>https://www.emix.com.pl</t>
-  </si>
-  <si>
     <t>Engelhardt &amp; Co AB, B.</t>
   </si>
   <si>
@@ -1093,18 +1018,6 @@
     <t>https://adetis-ingredients.fr</t>
   </si>
   <si>
-    <t>French for Edible Industries</t>
-  </si>
-  <si>
-    <t>Food industry — domain royalpack.net (food packaging)</t>
-  </si>
-  <si>
-    <t>6th of October,6th of October, Egypt</t>
-  </si>
-  <si>
-    <t>http://www.royalpack.net</t>
-  </si>
-  <si>
     <t>G C HAHN</t>
   </si>
   <si>
@@ -1321,15 +1234,6 @@
     <t>https://himfarminvest.com.ua</t>
   </si>
   <si>
-    <t>HOTEY Trading House, Private Business</t>
-  </si>
-  <si>
-    <t>+380 44 331 5415</t>
-  </si>
-  <si>
-    <t>http://hotey.in.ua</t>
-  </si>
-  <si>
     <t>IHC-I.H.Chempharm GmbH</t>
   </si>
   <si>
@@ -1423,18 +1327,6 @@
     <t>https://janus-services.com/</t>
   </si>
   <si>
-    <t>Kareva Marketing GmbH</t>
-  </si>
-  <si>
-    <t>Unclear — likely raw material trading/agency</t>
-  </si>
-  <si>
-    <t>+49 40 3690010</t>
-  </si>
-  <si>
-    <t>http://www.kareva.de</t>
-  </si>
-  <si>
     <t>Krátoška Chemin, spol. s r.o.</t>
   </si>
   <si>
@@ -1453,24 +1345,6 @@
     <t>https://www.kratoska.cz/</t>
   </si>
   <si>
-    <t>LA PATISSIERE</t>
-  </si>
-  <si>
-    <t>Pastry industry (explicit in name)</t>
-  </si>
-  <si>
-    <t>Ariana, Tunisia</t>
-  </si>
-  <si>
-    <t>+216 71 787 800</t>
-  </si>
-  <si>
-    <t>http://www.lapatissiere.com/</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/La-Patissi%C3%A9re-732923270132613/</t>
-  </si>
-  <si>
     <t>LABO-MIX SP. J. KRYSTYNA SKALKA, ANDRZEJ WENCLAW</t>
   </si>
   <si>
@@ -1570,21 +1444,6 @@
     <t>https://lirpasilicones.com/</t>
   </si>
   <si>
-    <t>LOMBARDI S.R.L.</t>
-  </si>
-  <si>
-    <t>BIENTINA, Italy</t>
-  </si>
-  <si>
-    <t>+39 0587 354365</t>
-  </si>
-  <si>
-    <t>info@lombardisrl.eu</t>
-  </si>
-  <si>
-    <t>https://www.lombardisrl.eu/</t>
-  </si>
-  <si>
     <t>Manuchar NV</t>
   </si>
   <si>
@@ -1672,18 +1531,6 @@
     <t>http://www.mido.com.eg</t>
   </si>
   <si>
-    <t>NAFTA-UKRAINA Ltd Ukrainian-Lithuanian JV</t>
-  </si>
-  <si>
-    <t>Petroleum &amp; chemical trading ('Nafta' = oil)</t>
-  </si>
-  <si>
-    <t>+380 44 510 4950</t>
-  </si>
-  <si>
-    <t>http://www.naftaukr.com</t>
-  </si>
-  <si>
     <t>Nano-Soda Україна, ПП</t>
   </si>
   <si>
@@ -1702,18 +1549,6 @@
     <t>https://nano-soda.com.ua/</t>
   </si>
   <si>
-    <t>Nippon Solvay K.K.</t>
-  </si>
-  <si>
-    <t>Industrial chemicals — Japanese subsidiary of Solvay Group (global inorganic chemical producer)</t>
-  </si>
-  <si>
-    <t>Minato-Ku, Tokyo, Japan</t>
-  </si>
-  <si>
-    <t>https://www.solvay.com/</t>
-  </si>
-  <si>
     <t>Nordiska Unipol AB</t>
   </si>
   <si>
@@ -1732,15 +1567,6 @@
     <t>https://nordiskaunipol.se/</t>
   </si>
   <si>
-    <t>NOVACHIM ROMANIA SRL</t>
-  </si>
-  <si>
-    <t>BUCURESTI, SECTOR 1, Romania</t>
-  </si>
-  <si>
-    <t>http://www.novachimromania.ro</t>
-  </si>
-  <si>
     <t>OANA CRISTAL COM SRL</t>
   </si>
   <si>
@@ -1897,24 +1723,6 @@
     <t>https://www.standard.pl</t>
   </si>
   <si>
-    <t>Quality Target</t>
-  </si>
-  <si>
-    <t>Unclear — possibly food quality/trading related</t>
-  </si>
-  <si>
-    <t>Borg El-Arab,Alexandria, Egypt</t>
-  </si>
-  <si>
-    <t>+20 3 459 5857</t>
-  </si>
-  <si>
-    <t>info@qualitytarget-eg.com</t>
-  </si>
-  <si>
-    <t>http://www.qualitytarget-eg.com</t>
-  </si>
-  <si>
     <t>REMY GmbH &amp; Co. KG</t>
   </si>
   <si>
@@ -2035,21 +1843,6 @@
     <t>https://www.salt.no</t>
   </si>
   <si>
-    <t>Shin Sanso Kagaku Co., Ltd.</t>
-  </si>
-  <si>
-    <t>Manufacture/distribution of industrial chemicals ('Kagaku' = chemistry in Japanese)</t>
-  </si>
-  <si>
-    <t>Tomakomai, Hokkaido, Japan</t>
-  </si>
-  <si>
-    <t>+81 144-55-7337</t>
-  </si>
-  <si>
-    <t>http://www.sskc.co.jp</t>
-  </si>
-  <si>
     <t>Snick Euroingredients NV</t>
   </si>
   <si>
@@ -2152,21 +1945,6 @@
     <t>https://www.spottrading.ro</t>
   </si>
   <si>
-    <t>SPT-CITRON Ltd</t>
-  </si>
-  <si>
-    <t>Kharkiv, Ukraine</t>
-  </si>
-  <si>
-    <t>+380 57 712 14 62</t>
-  </si>
-  <si>
-    <t>info@citron.kharkov.ua</t>
-  </si>
-  <si>
-    <t>http://www.citron.kharkov.ua</t>
-  </si>
-  <si>
     <t>Stanchem Sp. z o.o. Przedsiebiorstwo Chemiczne</t>
   </si>
   <si>
@@ -2476,24 +2254,6 @@
     <t>https://ziarnex.pl/</t>
   </si>
   <si>
-    <t>ZK</t>
-  </si>
-  <si>
-    <t>Unclear — domain zundel-kohler.com</t>
-  </si>
-  <si>
-    <t>ILLZACH, France</t>
-  </si>
-  <si>
-    <t>+33 3 89 45 49 12</t>
-  </si>
-  <si>
-    <t>contact@zundel-kohler.pro</t>
-  </si>
-  <si>
-    <t>https://www.zundel-kohler.pro/</t>
-  </si>
-  <si>
     <t>Аріста, ТПО, ТОВ</t>
   </si>
   <si>
@@ -2507,15 +2267,6 @@
   </si>
   <si>
     <t>https://arista.com.ua/</t>
-  </si>
-  <si>
-    <t>Реахімтранس, ТОВ</t>
-  </si>
-  <si>
-    <t>Chemical transport and distribution ('Reachem'+'Trans' in name)</t>
-  </si>
-  <si>
-    <t>https://reahimtrans.agrobiz.net/</t>
   </si>
   <si>
     <t>山西丰喜国际贸易有限公司</t>
@@ -2938,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="35" customWidth="1"/>
@@ -3088,10 +2839,10 @@
         <v>39</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>41</v>
@@ -3108,253 +2859,253 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>102</v>
@@ -3371,7 +3122,7 @@
         <v>105</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>8</v>
@@ -3380,172 +3131,172 @@
         <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3556,1041 +3307,1041 @@
         <v>146</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="H25" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="F26" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="G26" s="6" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="G27" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="C28" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="F32" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>170</v>
-      </c>
       <c r="G32" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="F40" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="G40" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E42" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="G42" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>211</v>
+        <v>8</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="A52" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="B52" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H52" s="4" t="s">
+      <c r="C52" s="6" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="D52" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="F52" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="G52" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>249</v>
+      <c r="C60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>260</v>
+        <v>33</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>261</v>
+        <v>33</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>33</v>
+        <v>207</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>33</v>
@@ -4599,50 +4350,50 @@
         <v>33</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>278</v>
+        <v>8</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>33</v>
@@ -4654,440 +4405,440 @@
         <v>9</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>33</v>
+        <v>297</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>33</v>
+        <v>207</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H73" s="7" t="s">
+      <c r="E73" s="2" t="s">
         <v>327</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>8</v>
+        <v>207</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>33</v>
+        <v>207</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>341</v>
+        <v>68</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>347</v>
+        <v>33</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>341</v>
+        <v>33</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>290</v>
+        <v>10</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>33</v>
+        <v>354</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>11</v>
+        <v>362</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>11</v>
+        <v>363</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>218</v>
+        <v>40</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>33</v>
+        <v>384</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>33</v>
@@ -5096,354 +4847,354 @@
         <v>9</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>10</v>
+        <v>385</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>8</v>
+        <v>391</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>218</v>
+        <v>398</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C86" s="3" t="s">
+      <c r="A86" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D88" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C88" s="3" t="s">
+      <c r="E88" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C89" s="6" t="s">
+      <c r="C90" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D90" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>424</v>
+      <c r="E90" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>427</v>
+        <v>8</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>33</v>
+        <v>441</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>11</v>
+        <v>444</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>444</v>
+        <v>8</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>10</v>
+        <v>460</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="G96" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="H96" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -5451,16 +5202,16 @@
         <v>461</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>33</v>
+        <v>462</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>462</v>
+        <v>240</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>463</v>
@@ -5480,1301 +5231,1301 @@
         <v>467</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>33</v>
+        <v>468</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>11</v>
+        <v>471</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="6" t="s">
+      <c r="A99" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D100" s="3" t="s">
+      <c r="E102" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>494</v>
+      <c r="E103" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>500</v>
+      <c r="A104" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C106" s="3" t="s">
+      <c r="A106" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="C107" s="6" t="s">
+      <c r="D107" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="H108" s="7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D107" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D108" s="3" t="s">
+      <c r="D109" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="E112" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="D115" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D109" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="C120" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="D120" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D122" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="G113" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C114" s="3" t="s">
+      <c r="E122" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D129" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G119" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="G121" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>599</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="G125" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>609</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>622</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="G129" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>629</v>
+      <c r="E129" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>33</v>
+        <v>468</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>421</v>
+        <v>562</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>636</v>
+        <v>33</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>510</v>
+        <v>8</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>642</v>
+        <v>33</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>510</v>
+        <v>33</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>510</v>
+        <v>8</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>33</v>
+        <v>668</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>603</v>
+        <v>669</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>656</v>
+        <v>11</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>657</v>
+        <v>676</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>658</v>
+        <v>677</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>660</v>
+        <v>679</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>662</v>
+        <v>681</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>663</v>
+        <v>682</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>664</v>
+        <v>683</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>666</v>
+        <v>685</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>204</v>
+        <v>138</v>
       </c>
       <c r="D138" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D143" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E138" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>667</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="D139" s="6" t="s">
+      <c r="E143" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D145" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E139" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>673</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>684</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>689</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>692</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="G144" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>706</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>707</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>708</v>
+      <c r="E145" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>33</v>
+        <v>722</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>710</v>
+        <v>425</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>510</v>
+        <v>33</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>620</v>
+        <v>425</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>33</v>
@@ -6783,621 +6534,127 @@
         <v>33</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>8</v>
+        <v>207</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>726</v>
+        <v>573</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>33</v>
+        <v>739</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>33</v>
+        <v>258</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>731</v>
+        <v>240</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="6" t="s">
+      <c r="A151" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D151" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E151" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>738</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>740</v>
+      <c r="E151" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D152" s="3" t="s">
+      <c r="A152" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="D152" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E152" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G153" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="H153" s="7" t="s">
+      <c r="E152" s="5" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="2" t="s">
+      <c r="F152" s="6" t="s">
         <v>752</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="G152" s="6" t="s">
         <v>753</v>
       </c>
-      <c r="C154" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E154" s="2" t="s">
+      <c r="H152" s="7" t="s">
         <v>754</v>
       </c>
-      <c r="F154" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E155" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="G155" s="6" t="s">
-        <v>762</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E157" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>769</v>
-      </c>
-      <c r="G157" s="6" t="s">
-        <v>770</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E159" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>778</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="H160" s="4" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>787</v>
-      </c>
-      <c r="G161" s="6" t="s">
-        <v>788</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="G163" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="H163" s="4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E164" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="G164" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="H164" s="7" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="G165" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="H165" s="4" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="F166" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="G166" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="H166" s="7" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="H167" s="4" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E168" s="5" t="s">
-        <v>819</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>820</v>
-      </c>
-      <c r="G168" s="6" t="s">
-        <v>821</v>
-      </c>
-      <c r="H168" s="7" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="H169" s="4" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D170" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="F170" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G170" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H170" s="7" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="F171" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="G171" s="6" t="s">
-        <v>836</v>
-      </c>
-      <c r="H171" s="7" t="s">
-        <v>837</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H171" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H152" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>